--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/cargas nuevas/Provision Contratos-RpySS - Octubre 2026.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/cargas nuevas/Provision Contratos-RpySS - Octubre 2026.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9BVRB40B5RA900012</t>
+          <t>9BVRB40B5RA593708</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>YV2XT4ZA1TA900112</t>
+          <t>YV2XT4ZA1TA276344</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>YV2TE2AB8RA900095</t>
+          <t>YV2TE2AB8RA543380</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9BVRT4ZD6PE900038</t>
+          <t>9BVRT4ZD6PE891576</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YV2XT4ZD6TE900125</t>
+          <t>YV2XT4ZD6TE839290</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9BVRB40B5RA900012</t>
+          <t>9BVRB40B5RA593708</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YV2XT4ZA1TA900112</t>
+          <t>YV2XT4ZA1TA276344</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>YV2TE2AB8RA900095</t>
+          <t>YV2TE2AB8RA543380</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9BVRT4ZD6PE900038</t>
+          <t>9BVRT4ZD6PE891576</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YV2XT4ZD6TE900125</t>
+          <t>YV2XT4ZD6TE839290</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YV2XT4ZA8SE900114</t>
+          <t>YV2XT4ZA8SE716676</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9BVRB40C1SE900013</t>
+          <t>9BVRB40C1SE434372</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9BVRT4ZC9TE900034</t>
+          <t>9BVRT4ZC9TE911626</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
